--- a/Specs/Specs_CDASH_CRFs_ChocolateTrial.xlsx
+++ b/Specs/Specs_CDASH_CRFs_ChocolateTrial.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0e4db44cd499522d/Desktop/ChocolateClinicalTrial_CDISC_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="11_F25DC773A252ABDACC1048B3215C69B25ADE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{964804D5-C72A-48AD-B503-E4A2F39CE4E8}"/>
+  <xr:revisionPtr revIDLastSave="183" documentId="11_F25DC773A252ABDACC1048B3215C69B25ADE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1C91954-4EB6-490F-9A36-7B9D10ED86DD}"/>
   <bookViews>
-    <workbookView xWindow="-48" yWindow="204" windowWidth="12204" windowHeight="12024" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="204" windowWidth="12204" windowHeight="12024" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DM" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="97">
   <si>
     <t>Type</t>
   </si>
@@ -369,7 +369,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -378,16 +378,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -836,7 +833,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6310A1-0E15-4EA2-A1D6-5FAE75CB175D}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" customWidth="1"/>
@@ -865,128 +862,114 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1</v>
+      <c r="A3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
+      <c r="A4" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>16</v>
+      <c r="D4" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
+      </c>
+      <c r="D5" s="5">
+        <v>37653</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="7">
-        <v>37653</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>46</v>
+      <c r="D7" s="4">
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>20</v>
+      <c r="A8" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="6">
-        <v>40</v>
+        <v>9</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>21</v>
+      <c r="A9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>22</v>
+      <c r="A10" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1035,7 +1018,7 @@
       <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1049,7 +1032,7 @@
       <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1077,7 +1060,7 @@
       <c r="C6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1091,7 +1074,7 @@
       <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1105,7 +1088,7 @@
       <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1119,7 +1102,7 @@
       <c r="C9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1196,7 +1179,7 @@
       <c r="C5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>37653</v>
       </c>
     </row>
